--- a/地点（ちてん）.xlsx
+++ b/地点（ちてん）.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\苗欣奕的东西\折跃\Japanese\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCAFF97F-6DDB-49DC-9C08-5F24A3420523}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21D03B49-1655-4E48-A1FE-6989F7212F16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="方向（ほうこう）" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,6 @@
     <sheet name="景勝区（けいしょうく）" sheetId="6" r:id="rId5"/>
     <sheet name="く" sheetId="4" r:id="rId6"/>
     <sheet name="道の駅（みちのえき）" sheetId="1" r:id="rId7"/>
-    <sheet name="句形（くけい）" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="749">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="747">
   <si>
     <t>大阪</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2758,14 +2757,6 @@
   </si>
   <si>
     <t>もくぞう</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>…之间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>郵便局は銀行と図書館の間「あいだ」にあります</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -3860,10 +3851,10 @@
         <v>94</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="18" x14ac:dyDescent="0.45">
@@ -3880,10 +3871,10 @@
         <v>24</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="18" x14ac:dyDescent="0.45">
@@ -3915,7 +3906,7 @@
         <v>44</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="N4" s="1" t="s">
         <v>364</v>
@@ -4074,10 +4065,10 @@
         <v>417</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="18" x14ac:dyDescent="0.45">
@@ -4097,7 +4088,7 @@
         <v>53</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="18" x14ac:dyDescent="0.45">
@@ -4132,7 +4123,7 @@
         <v>128</v>
       </c>
       <c r="O13" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="18" x14ac:dyDescent="0.45">
@@ -4155,7 +4146,7 @@
         <v>364</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="18" x14ac:dyDescent="0.45">
@@ -4180,10 +4171,10 @@
     </row>
     <row r="16" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="H16" s="1" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="L16" s="1" t="s">
         <v>352</v>
@@ -4197,10 +4188,10 @@
         <v>58</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="L17" s="1" t="s">
         <v>400</v>
@@ -4212,7 +4203,7 @@
         <v>401</v>
       </c>
       <c r="O17" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="18" x14ac:dyDescent="0.45">
@@ -4220,10 +4211,10 @@
         <v>59</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="L18" s="1" t="s">
         <v>22</v>
@@ -4240,13 +4231,13 @@
         <v>60</v>
       </c>
       <c r="H19" t="s">
+        <v>667</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="J19" s="1" t="s">
         <v>669</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>670</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>671</v>
       </c>
       <c r="L19" s="1" t="s">
         <v>587</v>
@@ -4533,10 +4524,10 @@
         <v>182</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="18" x14ac:dyDescent="0.45">
@@ -4547,13 +4538,13 @@
         <v>257</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>622</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>623</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>624</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1" t="s">
@@ -4574,10 +4565,10 @@
     </row>
     <row r="8" spans="1:18" ht="18" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>92</v>
@@ -4700,10 +4691,10 @@
     </row>
     <row r="13" spans="1:18" ht="18" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="M13" s="1" t="s">
         <v>494</v>
@@ -4829,7 +4820,7 @@
         <v>535</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>392</v>
@@ -4838,13 +4829,13 @@
         <v>393</v>
       </c>
       <c r="M19" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="O19" s="11" t="s">
         <v>638</v>
-      </c>
-      <c r="N19" s="1" t="s">
-        <v>639</v>
-      </c>
-      <c r="O19" s="11" t="s">
-        <v>640</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="18" x14ac:dyDescent="0.45">
@@ -4861,13 +4852,13 @@
         <v>217</v>
       </c>
       <c r="M20" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="O20" s="1" t="s">
         <v>641</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>642</v>
-      </c>
-      <c r="O20" s="1" t="s">
-        <v>643</v>
       </c>
     </row>
     <row r="21" spans="1:15" ht="18" x14ac:dyDescent="0.45">
@@ -4885,10 +4876,10 @@
       </c>
       <c r="M21" s="1"/>
       <c r="N21" s="1" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="O21" s="12" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
     </row>
     <row r="22" spans="1:15" ht="18" x14ac:dyDescent="0.45">
@@ -5049,10 +5040,10 @@
         <v>208</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="18" x14ac:dyDescent="0.45">
@@ -5178,7 +5169,7 @@
         <v>568</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="18" x14ac:dyDescent="0.45">
@@ -5206,10 +5197,10 @@
         <v>595</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="18" x14ac:dyDescent="0.45">
@@ -5220,15 +5211,15 @@
         <v>594</v>
       </c>
       <c r="C44" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="18" x14ac:dyDescent="0.45">
       <c r="A45" s="1" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>608</v>
@@ -5242,120 +5233,120 @@
     </row>
     <row r="46" spans="1:7" ht="18" x14ac:dyDescent="0.45">
       <c r="A46" s="1" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="18" x14ac:dyDescent="0.45">
       <c r="A47" s="1" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="18" x14ac:dyDescent="0.45">
       <c r="A48" s="1" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="18" x14ac:dyDescent="0.45">
       <c r="A49" s="1" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="E49" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="G49" s="1" t="s">
         <v>746</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>747</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>748</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="18" x14ac:dyDescent="0.45">
       <c r="A50" s="1" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="18" x14ac:dyDescent="0.45">
       <c r="A51" s="1" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="18" x14ac:dyDescent="0.45">
       <c r="A52" s="1" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="18" x14ac:dyDescent="0.45">
       <c r="A53" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="C53" s="1" t="s">
         <v>721</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>722</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>723</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="18" x14ac:dyDescent="0.45">
       <c r="A54" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>735</v>
+      </c>
+      <c r="C54" s="6" t="s">
         <v>736</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>737</v>
-      </c>
-      <c r="C54" s="6" t="s">
-        <v>738</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="18" x14ac:dyDescent="0.45">
       <c r="A55" s="1" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="18" x14ac:dyDescent="0.45">
       <c r="A56" s="1" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
     </row>
   </sheetData>
@@ -5382,7 +5373,7 @@
         <v>172</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>178</v>
@@ -5431,13 +5422,13 @@
         <v>121</v>
       </c>
       <c r="H4" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>658</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>659</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>660</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="18" x14ac:dyDescent="0.45">
@@ -5454,13 +5445,13 @@
         <v>273</v>
       </c>
       <c r="H5" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>696</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>697</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>698</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="18" x14ac:dyDescent="0.45">
@@ -5477,13 +5468,13 @@
         <v>275</v>
       </c>
       <c r="H6" t="s">
+        <v>659</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="J6" s="11" t="s">
         <v>661</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>662</v>
-      </c>
-      <c r="J6" s="11" t="s">
-        <v>663</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="18" x14ac:dyDescent="0.45">
@@ -5503,13 +5494,13 @@
         <v>300</v>
       </c>
       <c r="H7" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="J7" s="1" t="s">
         <v>664</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>665</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>666</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="18" x14ac:dyDescent="0.45">
@@ -5526,10 +5517,10 @@
         <v>205</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="18" x14ac:dyDescent="0.45">
@@ -5666,13 +5657,13 @@
     </row>
     <row r="15" spans="1:12" ht="18" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="C15" t="s">
         <v>679</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>680</v>
-      </c>
-      <c r="C15" t="s">
-        <v>681</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>465</v>
@@ -5689,13 +5680,13 @@
     </row>
     <row r="16" spans="1:12" ht="18" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="C16" t="s">
         <v>682</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>683</v>
-      </c>
-      <c r="C16" t="s">
-        <v>684</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>492</v>
@@ -5712,19 +5703,19 @@
     </row>
     <row r="17" spans="1:10" ht="18" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C17" t="s">
         <v>693</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>694</v>
-      </c>
-      <c r="C17" t="s">
-        <v>695</v>
-      </c>
       <c r="D17" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>488</v>
@@ -5735,16 +5726,16 @@
     </row>
     <row r="18" spans="1:10" ht="18" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>548</v>
@@ -5758,10 +5749,10 @@
     </row>
     <row r="19" spans="1:10" ht="18" x14ac:dyDescent="0.45">
       <c r="D19" s="1" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>596</v>
@@ -5781,43 +5772,43 @@
         <v>491</v>
       </c>
       <c r="H20" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="J20" t="s">
         <v>676</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>677</v>
-      </c>
-      <c r="J20" t="s">
-        <v>678</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="18" x14ac:dyDescent="0.45">
       <c r="D21" s="1" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="18" x14ac:dyDescent="0.45">
       <c r="H22" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="18" x14ac:dyDescent="0.45">
       <c r="H23" s="1" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
     </row>
   </sheetData>
@@ -6041,10 +6032,10 @@
         <v>505</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="18" x14ac:dyDescent="0.45">
@@ -6076,10 +6067,10 @@
     </row>
     <row r="15" spans="1:14" ht="18" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
     </row>
   </sheetData>
@@ -6159,21 +6150,21 @@
     </row>
     <row r="9" spans="1:3" ht="18" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="18" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>701</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>702</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>703</v>
       </c>
     </row>
   </sheetData>
@@ -6655,26 +6646,7 @@
     </row>
     <row r="26" spans="1:2" ht="18" x14ac:dyDescent="0.45">
       <c r="B26" s="1" t="s">
-        <v>621</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{016684FE-987B-4D5C-8A7A-D8EBFEA4FE32}">
-  <dimension ref="A2:B2"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="2" spans="1:2" ht="18" x14ac:dyDescent="0.45">
-      <c r="A2" s="7" t="s">
-        <v>617</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
   </sheetData>
